--- a/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_2/CF_M05_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,151 +471,201 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture, acting as a central traffic management point.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bus d’integració</t>
+          <t>C_01, C_02, C_04, R_33, R_34, R_35, R_39, R_40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_13, P_03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bus d’integració</t>
+          <t>10a. Appearance; 11a. Usability; 11c. Learning; El nou contingut ha de mantenir una coherència visual amb el disseny de l’antiga versió de l’aplicació.; El disseny, colors, tipografies i organització han de ser consistents amb l’antiga versió.; El sistema ha de ser fàcil d’utilitzar per a qualsevol usuari; L’usuari ha de poder efectuar les noves operacions sense formació especial.; El temps d’aprenentatge per les noves funcionalitats no hauria de superar els 5 min.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leader Service</t>
+          <t>Angular; MVVM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.703</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Access Control microservice has as its main objective the management of user authentication and their permissions within the application.</t>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R_48</t>
+          <t>C_05, C_06, C_07, R_41, R_42, R_43, R_44, R_45, R_46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_14, P_04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>El sistema ha de disposar d’un mecanisme segur d’autenticació i verificació de permisos per assegurar que cada usuari només pugui accedir a la informació i funcionalitats que li corresponen.</t>
+          <t>12a. Speed and latency; 12a. Availability; 12f. Capacity; Les operacions de consulta han de tenir un temps de càrrega inferior a 1 segon.; Temps de resposta no ha superar 1 segon en el 95% de les consultes.; L’aplicació web ha de garantir un funcionament continu i estable, assegurant la seva disponibilitat en qualsevol moment.; La disponibilitat del sistema ha de ser de mínim 99,9%, fins i tot durant els moments d’ús intensiu.; L’aplicació web ha de suportar un gran nombre d’usuaris simultanis sense degradar el seu rendiment.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Access Control Service</t>
+          <t>Spring Boot; Layered Architecture</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7119</v>
+        <v>0.7287</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services, which allows building modern single-page applications (SPA) that render dynamic views and manage internal navigation without having to reload the page, improving fluidity of use.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, that formulates service requests, and the server, that receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_02, C_04</t>
+          <t>C_05, C_06, R_43, R_44, R_45, R_46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AU_13, P_03</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>61, 62</t>
+          <t>60, 61</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11a. Usability; 11c. Learning</t>
+          <t>12a. Speed and latency; 12a. Availability; L’aplicació web ha de garantir un funcionament continu i estable, assegurant la seva disponibilitat en qualsevol moment.; La disponibilitat del sistema ha de ser de mínim 99,9%, fins i tot durant els moments d’ús intensiu.; L’aplicació web ha de suportar un gran nombre d’usuaris simultanis sense degradar el seu rendiment.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Angular; MVVM</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.7437</v>
+        <v>0.7099</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. One of the great advantages of AWS is that it has a very wide selection of services: from the deployment of servers and databases, to AI, storage, security, and specific services for sectors. This diversity makes it easy to adapt to the needs of the project, allows growing and scaling the project in an agile way and eliminates the need to look for other platforms when requirements evolve. For this reason, AWS was chosen instead of other options like Google Cloud Platform or Microsoft Azure. Having so many services available leaves the effort to be concentrated on the development of the solution, without having to invest extra time in infrastructure issues. Another reason why AWS was chosen was that this platform invests heavily in security and certifications, manages multiple security levels and offers tools to protect data and infrastructure, facilitating compliance with legal regulations and international standards.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C_06, C_07, R_43, R_44, R_45, R_46</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_17, AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>81, 82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12a. Availability; 12f. Capacity; L’aplicació web ha de garantir un funcionament continu i estable, assegurant la seva disponibilitat en qualsevol moment.; La disponibilitat del sistema ha de ser de mínim 99,9%, fins i tot durant els moments d’ús intensiu.; L’aplicació web ha de suportar un gran nombre d’usuaris simultanis sense degradar el seu rendiment.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS); Amazon EKS; Kubernetes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7302</v>
       </c>
     </row>
   </sheetData>
